--- a/data/trans_dic/IP31KM03_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM03_2023-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>79,51%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>76,76; 91,55</t>
+          <t>66,32; 84,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>67,69; 85,24</t>
+          <t>74,2; 89,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>75,12; 86,73</t>
+          <t>72,26; 84,98</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>70,01%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>73,39%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>73,88; 92,46</t>
+          <t>62,01; 77,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>61,2; 77,92</t>
+          <t>69,12; 84,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70,82; 84,33</t>
+          <t>67,85; 78,58</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,0%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>74,34; 89,57</t>
+          <t>80,73; 94,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>81,58; 94,03</t>
+          <t>73,51; 89,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>80,92; 90,96</t>
+          <t>80,18; 90,48</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>61,75; 80,87</t>
+          <t>71,79; 91,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>71,14; 91,6</t>
+          <t>62,24; 82,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>70,97; 84,93</t>
+          <t>70,21; 84,51</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,21%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>88,1; 99,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>88,11; 99,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>94,64; 99,57</t>
+          <t>94,81; 99,66</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>74,18%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>59,05; 79,41</t>
+          <t>68,96; 87,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>69,69; 87,44</t>
+          <t>58,52; 79,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>69,12; 82,39</t>
+          <t>66,74; 80,42</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>81,7%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>77,7; 89,6</t>
+          <t>72,13; 85,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>73,36; 85,93</t>
+          <t>78,51; 89,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>77,57; 86,09</t>
+          <t>77,06; 85,89</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,94%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>92,66; 98,33</t>
+          <t>91,66; 98,15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>92,08; 98,12</t>
+          <t>92,59; 98,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>93,59; 97,74</t>
+          <t>93,4; 97,69</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>83,79%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>82,04; 87,31</t>
+          <t>80,68; 85,98</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>80,89; 86,24</t>
+          <t>81,56; 86,46</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>82,36; 86,07</t>
+          <t>82,03; 85,62</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>76</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>61489</t>
+          <t>45805</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>58018</t>
+          <t>45780</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>119507</t>
+          <t>91586</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>54809; 65367</t>
+          <t>39966; 51066</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>50502; 63591</t>
+          <t>40751; 49358</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>109678; 126632</t>
+          <t>83231; 97890</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>103434</t>
+          <t>80477</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>89049</t>
+          <t>76785</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>192482</t>
+          <t>157262</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>92825; 116177</t>
+          <t>71279; 89352</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>77368; 98513</t>
+          <t>68661; 83439</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>178528; 212577</t>
+          <t>145384; 168377</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>76</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>46067</t>
+          <t>51058</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>57665</t>
+          <t>44758</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>103733</t>
+          <t>95816</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>41298; 49758</t>
+          <t>46259; 53988</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>52728; 60773</t>
+          <t>39776; 48384</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>97249; 109318</t>
+          <t>89325; 100810</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>68</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>50798</t>
+          <t>57980</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>62840</t>
+          <t>51910</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>113638</t>
+          <t>109890</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>43026; 56355</t>
+          <t>50124; 63877</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>53614; 69039</t>
+          <t>43858; 58040</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>102948; 123194</t>
+          <t>98490; 118552</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>64</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>32803</t>
+          <t>39579</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>34025</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>73522</t>
+          <t>73604</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>30131; 33888</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>31165; 35116</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>70905; 74600</t>
+          <t>71059; 74692</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>52</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>31051</t>
+          <t>37426</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>42774</t>
+          <t>30447</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>73825</t>
+          <t>67873</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>26153; 35171</t>
+          <t>32553; 41097</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>37483; 47027</t>
+          <t>25917; 35008</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>67784; 80800</t>
+          <t>61068; 73578</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>147</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>104130</t>
+          <t>111065</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>125184</t>
+          <t>103310</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>229314</t>
+          <t>214376</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>96107; 110833</t>
+          <t>101400; 119827</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>113739; 133232</t>
+          <t>95644; 108907</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>216211; 239971</t>
+          <t>202199; 225370</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>177</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>123733</t>
+          <t>150332</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>147805</t>
+          <t>132726</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>271536</t>
+          <t>283058</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>119227; 126518</t>
+          <t>144029; 154233</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>141945; 151261</t>
+          <t>127680; 135588</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>264693; 276435</t>
+          <t>275572; 288234</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>784</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>769</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>784</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>553504</t>
+          <t>573722</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>624054</t>
+          <t>519742</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1177558</t>
+          <t>1093463</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>535855; 570235</t>
+          <t>554146; 590560</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>602396; 642254</t>
+          <t>504214; 534529</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1151284; 1203148</t>
+          <t>1070568; 1117360</t>
         </is>
       </c>
     </row>
